--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30103/BU01/HRM/post DFS_HRM-2031-0332/Panel 02/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30103/BU01/HRM/post DFS_HRM-2031-0332/Panel 02/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Back_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.57936</v>
+        <v>16.74237</v>
       </c>
       <c r="D2" t="n">
-        <v>16.72007</v>
+        <v>16.42784</v>
       </c>
       <c r="E2" t="n">
-        <v>16.47027</v>
+        <v>16.62254</v>
       </c>
       <c r="F2" t="n">
-        <v>42.20743</v>
+        <v>42.47919</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05095</v>
+        <v>0.05011</v>
       </c>
       <c r="H2" t="n">
-        <v>1.83514</v>
+        <v>1.80515</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.17306</v>
+        <v>16.65657</v>
       </c>
       <c r="D3" t="n">
-        <v>16.54268</v>
+        <v>16.40137</v>
       </c>
       <c r="E3" t="n">
-        <v>16.61587</v>
+        <v>16.61704</v>
       </c>
       <c r="F3" t="n">
-        <v>42.42764</v>
+        <v>42.5907</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05042</v>
+        <v>0.04929</v>
       </c>
       <c r="H3" t="n">
-        <v>1.82144</v>
+        <v>1.7807</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.49401</v>
+        <v>16.60539</v>
       </c>
       <c r="D4" t="n">
-        <v>16.4213</v>
+        <v>16.44921</v>
       </c>
       <c r="E4" t="n">
-        <v>16.87256</v>
+        <v>16.50732</v>
       </c>
       <c r="F4" t="n">
-        <v>42.60667</v>
+        <v>43.43517</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05134</v>
+        <v>0.0509</v>
       </c>
       <c r="H4" t="n">
-        <v>1.80677</v>
+        <v>1.81116</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.60498</v>
+        <v>16.75402</v>
       </c>
       <c r="D5" t="n">
-        <v>16.69835</v>
+        <v>16.45478</v>
       </c>
       <c r="E5" t="n">
-        <v>16.37455</v>
+        <v>16.56012</v>
       </c>
       <c r="F5" t="n">
-        <v>41.57915</v>
+        <v>42.92166</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04985</v>
+        <v>0.04929</v>
       </c>
       <c r="H5" t="n">
-        <v>1.79874</v>
+        <v>1.81143</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.39955</v>
+        <v>16.52358</v>
       </c>
       <c r="D6" t="n">
-        <v>16.55361</v>
+        <v>16.39758</v>
       </c>
       <c r="E6" t="n">
-        <v>16.89795</v>
+        <v>16.41783</v>
       </c>
       <c r="F6" t="n">
-        <v>42.84623</v>
+        <v>41.77114</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05132</v>
+        <v>0.05124</v>
       </c>
       <c r="H6" t="n">
-        <v>1.80173</v>
+        <v>1.81845</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.84364</v>
+        <v>16.73169</v>
       </c>
       <c r="D7" t="n">
-        <v>16.34299</v>
+        <v>16.48254</v>
       </c>
       <c r="E7" t="n">
-        <v>16.49914</v>
+        <v>16.65758</v>
       </c>
       <c r="F7" t="n">
-        <v>42.0377</v>
+        <v>41.96602</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05105</v>
+        <v>0.04953</v>
       </c>
       <c r="H7" t="n">
-        <v>1.79988</v>
+        <v>1.82308</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.43976</v>
+        <v>16.75061</v>
       </c>
       <c r="D8" t="n">
-        <v>16.4823</v>
+        <v>16.50573</v>
       </c>
       <c r="E8" t="n">
-        <v>16.96835</v>
+        <v>16.7381</v>
       </c>
       <c r="F8" t="n">
-        <v>42.38727</v>
+        <v>42.36952</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0508</v>
+        <v>0.05017</v>
       </c>
       <c r="H8" t="n">
-        <v>1.79896</v>
+        <v>1.80033</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.62443</v>
+        <v>16.83825</v>
       </c>
       <c r="D9" t="n">
-        <v>16.78224</v>
+        <v>16.37159</v>
       </c>
       <c r="E9" t="n">
-        <v>16.57251</v>
+        <v>16.6221</v>
       </c>
       <c r="F9" t="n">
-        <v>42.08279</v>
+        <v>42.54845</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05072</v>
+        <v>0.04953</v>
       </c>
       <c r="H9" t="n">
-        <v>1.83721</v>
+        <v>1.82921</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.54497</v>
+        <v>16.70087</v>
       </c>
       <c r="D10" t="n">
-        <v>16.5127</v>
+        <v>16.16175</v>
       </c>
       <c r="E10" t="n">
-        <v>16.61272</v>
+        <v>16.60594</v>
       </c>
       <c r="F10" t="n">
-        <v>43.02891</v>
+        <v>42.34091</v>
       </c>
       <c r="G10" t="n">
-        <v>0.04949</v>
+        <v>0.05066</v>
       </c>
       <c r="H10" t="n">
-        <v>1.82022</v>
+        <v>1.80808</v>
       </c>
     </row>
     <row r="11">
@@ -696,12 +696,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -713,8 +718,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Trace 1</t>
-        </is>
+          <t>Pad 2</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>16.76767</v>
+      </c>
+      <c r="D12" t="n">
+        <v>16.53488</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16.62916</v>
+      </c>
+      <c r="F12" t="n">
+        <v>42.25308</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.05011</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.8074</v>
       </c>
     </row>
     <row r="13">
@@ -723,6 +746,24 @@
           <t>Unit 8</t>
         </is>
       </c>
+      <c r="C13" t="n">
+        <v>16.65926</v>
+      </c>
+      <c r="D13" t="n">
+        <v>16.63689</v>
+      </c>
+      <c r="E13" t="n">
+        <v>16.63699</v>
+      </c>
+      <c r="F13" t="n">
+        <v>42.10936</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.04883</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.82926</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -730,6 +771,24 @@
           <t>Unit 9</t>
         </is>
       </c>
+      <c r="C14" t="n">
+        <v>16.69556</v>
+      </c>
+      <c r="D14" t="n">
+        <v>15.85087</v>
+      </c>
+      <c r="E14" t="n">
+        <v>16.61406</v>
+      </c>
+      <c r="F14" t="n">
+        <v>42.13983</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.05051</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.8227</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -737,6 +796,24 @@
           <t>Unit 4</t>
         </is>
       </c>
+      <c r="C15" t="n">
+        <v>16.77474</v>
+      </c>
+      <c r="D15" t="n">
+        <v>16.42121</v>
+      </c>
+      <c r="E15" t="n">
+        <v>16.45935</v>
+      </c>
+      <c r="F15" t="n">
+        <v>42.16102</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.0498</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.80907</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -744,6 +821,24 @@
           <t>Unit 5</t>
         </is>
       </c>
+      <c r="C16" t="n">
+        <v>16.99091</v>
+      </c>
+      <c r="D16" t="n">
+        <v>16.59242</v>
+      </c>
+      <c r="E16" t="n">
+        <v>16.64223</v>
+      </c>
+      <c r="F16" t="n">
+        <v>41.66868</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.05051</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.76641</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -751,6 +846,24 @@
           <t>Unit 6</t>
         </is>
       </c>
+      <c r="C17" t="n">
+        <v>16.88671</v>
+      </c>
+      <c r="D17" t="n">
+        <v>16.50106</v>
+      </c>
+      <c r="E17" t="n">
+        <v>16.62728</v>
+      </c>
+      <c r="F17" t="n">
+        <v>41.97811</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.04977</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.80914</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -758,6 +871,24 @@
           <t>Unit 1</t>
         </is>
       </c>
+      <c r="C18" t="n">
+        <v>16.75756</v>
+      </c>
+      <c r="D18" t="n">
+        <v>16.50555</v>
+      </c>
+      <c r="E18" t="n">
+        <v>16.53352</v>
+      </c>
+      <c r="F18" t="n">
+        <v>42.32027</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.04924</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.83306</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -765,12 +896,974 @@
           <t>Unit 2</t>
         </is>
       </c>
+      <c r="C19" t="n">
+        <v>16.92456</v>
+      </c>
+      <c r="D19" t="n">
+        <v>16.26455</v>
+      </c>
+      <c r="E19" t="n">
+        <v>16.65953</v>
+      </c>
+      <c r="F19" t="n">
+        <v>42.17869</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.05008</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.7935</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
           <t>Unit 3</t>
         </is>
+      </c>
+      <c r="C20" t="n">
+        <v>16.65485</v>
+      </c>
+      <c r="D20" t="n">
+        <v>16.41903</v>
+      </c>
+      <c r="E20" t="n">
+        <v>16.57449</v>
+      </c>
+      <c r="F20" t="n">
+        <v>42.27816</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.05026</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.83879</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SR Pad 1</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>15.57925</v>
+      </c>
+      <c r="D22" t="n">
+        <v>15.37308</v>
+      </c>
+      <c r="E22" t="n">
+        <v>15.46351</v>
+      </c>
+      <c r="F22" t="n">
+        <v>249.65216</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>15.67653</v>
+      </c>
+      <c r="D23" t="n">
+        <v>15.24646</v>
+      </c>
+      <c r="E23" t="n">
+        <v>15.34288</v>
+      </c>
+      <c r="F23" t="n">
+        <v>256.43983</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>15.96199</v>
+      </c>
+      <c r="D24" t="n">
+        <v>15.29809</v>
+      </c>
+      <c r="E24" t="n">
+        <v>15.85231</v>
+      </c>
+      <c r="F24" t="n">
+        <v>253.35731</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>15.63534</v>
+      </c>
+      <c r="D25" t="n">
+        <v>15.25187</v>
+      </c>
+      <c r="E25" t="n">
+        <v>15.54179</v>
+      </c>
+      <c r="F25" t="n">
+        <v>249.66204</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>15.79312</v>
+      </c>
+      <c r="D26" t="n">
+        <v>15.39218</v>
+      </c>
+      <c r="E26" t="n">
+        <v>15.50864</v>
+      </c>
+      <c r="F26" t="n">
+        <v>254.64176</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>15.91905</v>
+      </c>
+      <c r="D27" t="n">
+        <v>15.41024</v>
+      </c>
+      <c r="E27" t="n">
+        <v>15.53987</v>
+      </c>
+      <c r="F27" t="n">
+        <v>252.32904</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>15.68738</v>
+      </c>
+      <c r="D28" t="n">
+        <v>15.155</v>
+      </c>
+      <c r="E28" t="n">
+        <v>15.62612</v>
+      </c>
+      <c r="F28" t="n">
+        <v>254.2292</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>15.52393</v>
+      </c>
+      <c r="D29" t="n">
+        <v>15.18401</v>
+      </c>
+      <c r="E29" t="n">
+        <v>15.42173</v>
+      </c>
+      <c r="F29" t="n">
+        <v>248.21409</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>15.60217</v>
+      </c>
+      <c r="D30" t="n">
+        <v>15.21481</v>
+      </c>
+      <c r="E30" t="n">
+        <v>15.57288</v>
+      </c>
+      <c r="F30" t="n">
+        <v>256.13823</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Trace 1</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>16.6134</v>
+      </c>
+      <c r="D32" t="n">
+        <v>15.85621</v>
+      </c>
+      <c r="E32" t="n">
+        <v>16.3429</v>
+      </c>
+      <c r="F32" t="n">
+        <v>21.66129</v>
+      </c>
+      <c r="G32" t="n">
+        <v>34.52577</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>17.29605</v>
+      </c>
+      <c r="D33" t="n">
+        <v>15.73591</v>
+      </c>
+      <c r="E33" t="n">
+        <v>16.40262</v>
+      </c>
+      <c r="F33" t="n">
+        <v>22.29939</v>
+      </c>
+      <c r="G33" t="n">
+        <v>33.91555</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>16.99756</v>
+      </c>
+      <c r="D34" t="n">
+        <v>16.07947</v>
+      </c>
+      <c r="E34" t="n">
+        <v>16.33134</v>
+      </c>
+      <c r="F34" t="n">
+        <v>21.7498</v>
+      </c>
+      <c r="G34" t="n">
+        <v>34.69095</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>16.78855</v>
+      </c>
+      <c r="D35" t="n">
+        <v>16.04494</v>
+      </c>
+      <c r="E35" t="n">
+        <v>16.10124</v>
+      </c>
+      <c r="F35" t="n">
+        <v>21.82039</v>
+      </c>
+      <c r="G35" t="n">
+        <v>33.57786</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>16.61786</v>
+      </c>
+      <c r="D36" t="n">
+        <v>15.9886</v>
+      </c>
+      <c r="E36" t="n">
+        <v>16.35489</v>
+      </c>
+      <c r="F36" t="n">
+        <v>21.57722</v>
+      </c>
+      <c r="G36" t="n">
+        <v>34.4973</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>16.74078</v>
+      </c>
+      <c r="D37" t="n">
+        <v>15.5848</v>
+      </c>
+      <c r="E37" t="n">
+        <v>15.7996</v>
+      </c>
+      <c r="F37" t="n">
+        <v>21.54558</v>
+      </c>
+      <c r="G37" t="n">
+        <v>33.38791</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>16.7533</v>
+      </c>
+      <c r="D38" t="n">
+        <v>15.65886</v>
+      </c>
+      <c r="E38" t="n">
+        <v>16.4496</v>
+      </c>
+      <c r="F38" t="n">
+        <v>21.55537</v>
+      </c>
+      <c r="G38" t="n">
+        <v>34.07728</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>16.52059</v>
+      </c>
+      <c r="D39" t="n">
+        <v>15.76911</v>
+      </c>
+      <c r="E39" t="n">
+        <v>16.10715</v>
+      </c>
+      <c r="F39" t="n">
+        <v>21.91259</v>
+      </c>
+      <c r="G39" t="n">
+        <v>34.50607</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>16.56081</v>
+      </c>
+      <c r="D40" t="n">
+        <v>15.78275</v>
+      </c>
+      <c r="E40" t="n">
+        <v>16.17457</v>
+      </c>
+      <c r="F40" t="n">
+        <v>21.7442</v>
+      </c>
+      <c r="G40" t="n">
+        <v>33.70122</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Trace 2</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>16.70639</v>
+      </c>
+      <c r="D42" t="n">
+        <v>16.05629</v>
+      </c>
+      <c r="E42" t="n">
+        <v>16.33454</v>
+      </c>
+      <c r="F42" t="n">
+        <v>21.39016</v>
+      </c>
+      <c r="G42" t="n">
+        <v>33.47729</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>16.49343</v>
+      </c>
+      <c r="D43" t="n">
+        <v>15.62259</v>
+      </c>
+      <c r="E43" t="n">
+        <v>16.37359</v>
+      </c>
+      <c r="F43" t="n">
+        <v>21.71303</v>
+      </c>
+      <c r="G43" t="n">
+        <v>33.81647</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>16.61337</v>
+      </c>
+      <c r="D44" t="n">
+        <v>15.78552</v>
+      </c>
+      <c r="E44" t="n">
+        <v>16.35386</v>
+      </c>
+      <c r="F44" t="n">
+        <v>21.78347</v>
+      </c>
+      <c r="G44" t="n">
+        <v>33.26778</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>16.47911</v>
+      </c>
+      <c r="D45" t="n">
+        <v>15.90127</v>
+      </c>
+      <c r="E45" t="n">
+        <v>16.06748</v>
+      </c>
+      <c r="F45" t="n">
+        <v>21.40312</v>
+      </c>
+      <c r="G45" t="n">
+        <v>33.77659</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>16.75064</v>
+      </c>
+      <c r="D46" t="n">
+        <v>16.40563</v>
+      </c>
+      <c r="E46" t="n">
+        <v>16.42987</v>
+      </c>
+      <c r="F46" t="n">
+        <v>21.49129</v>
+      </c>
+      <c r="G46" t="n">
+        <v>34.62261</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>16.6707</v>
+      </c>
+      <c r="D47" t="n">
+        <v>15.86278</v>
+      </c>
+      <c r="E47" t="n">
+        <v>16.05848</v>
+      </c>
+      <c r="F47" t="n">
+        <v>21.59675</v>
+      </c>
+      <c r="G47" t="n">
+        <v>33.32697</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>16.45979</v>
+      </c>
+      <c r="D48" t="n">
+        <v>15.84735</v>
+      </c>
+      <c r="E48" t="n">
+        <v>16.41828</v>
+      </c>
+      <c r="F48" t="n">
+        <v>21.49397</v>
+      </c>
+      <c r="G48" t="n">
+        <v>34.07827</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>16.85877</v>
+      </c>
+      <c r="D49" t="n">
+        <v>15.82145</v>
+      </c>
+      <c r="E49" t="n">
+        <v>16.42663</v>
+      </c>
+      <c r="F49" t="n">
+        <v>20.82584</v>
+      </c>
+      <c r="G49" t="n">
+        <v>33.96383</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>16.82885</v>
+      </c>
+      <c r="D50" t="n">
+        <v>15.94415</v>
+      </c>
+      <c r="E50" t="n">
+        <v>16.1523</v>
+      </c>
+      <c r="F50" t="n">
+        <v>21.28017</v>
+      </c>
+      <c r="G50" t="n">
+        <v>33.70515</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>via 1</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.60088</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1.09792</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.60292</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1.09554</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.60937</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1.08706</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0.6039600000000001</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1.09596</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0.61952</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1.11273</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0.59776</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1.10769</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.61578</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1.09865</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.60261</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1.10356</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.61081</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1.1074</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>via 2</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.60267</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1.11848</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0.59681</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1.11128</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0.5963000000000001</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1.09529</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0.59672</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1.09182</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0.59765</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1.09133</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0.60848</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1.09337</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0.6052999999999999</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1.11234</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0.60527</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1.09883</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0.58887</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1.13286</v>
       </c>
     </row>
   </sheetData>
